--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0168.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0168.xlsx
@@ -10519,7 +10519,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Xong việc rồi! Tự do ngọt ngào đây rồi! Kì nghỉ mát, ta đến đây!</t>
+          <t>Xong việc rồi! Tự do ngọt ngào đây rồi! Kì nghỉ mát, tao đến đây!</t>
         </is>
       </c>
     </row>
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Xem mấy tấm hình đỉnh nhất trong kỳ nghỉ của ta này... gửi ngay kiệt tác này cho Revan. Đánh dấu "khẩn cấp" nhé.</t>
+          <t>Xem mấy tấm hình đỉnh nhất trong kỳ nghỉ của tao này... gửi ngay kiệt tác này cho Revan. Đánh dấu "khẩn cấp" nhé.</t>
         </is>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Khẩn cấp á? Thật sự hả? Lương tâm cậu không cắn rứt chút nào à?</t>
+          <t>Khẩn cấp á? Thật sự hả? Lương tâm mày không cắn rứt chút nào à?</t>
         </is>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Không phải ta.</t>
+          <t>Không phải tao.</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Ta không nghĩ vậy...</t>
+          <t>Tao không nghĩ vậy...</t>
         </is>
       </c>
     </row>
@@ -11559,7 +11559,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Ta bảo ngươi rồi, đám nhân viên hỗ trợ đang giấu một bí mật khổng lồ!</t>
+          <t>Tao bảo mày rồi, đám nhân viên hỗ trợ đang giấu một bí mật khổng lồ!</t>
         </is>
       </c>
     </row>
@@ -12339,7 +12339,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Xu thì ta hiểu, nhưng sách giáo khoa là cái quái gì vậy?</t>
+          <t>Xu thì tao hiểu, nhưng sách giáo khoa là cái quái gì vậy?</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Cái này của Cục Khoa học Năng lượng Ánh sáng đấy. Có cả tên người nhận luôn. Để ta gọi hắn đến lấy...</t>
+          <t>Cái này của Cục Khoa học Năng lượng Ánh sáng đấy. Có cả tên người nhận luôn. Để tao gọi hắn đến lấy...</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Ta nghe nói mì hút hết nước rồi tắc cả buồng chứa. Hóa đơn sửa chắc đắt kinh khủng!</t>
+          <t>Tao nghe nói mì hút hết nước rồi tắc cả buồng chứa. Hóa đơn sửa chắc đắt kinh khủng!</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Cậu thực sự nghĩ vậy sao? Ta không tin đâu… Hả? Revan vừa trả lời rồi. Lại gấp nữa. Để xem nào…</t>
+          <t>Cậu thực sự nghĩ vậy sao? Tao không tin đâu… Hả? Revan vừa trả lời rồi. Lại gấp nữa. Để xem nào…</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>"—Tình bạn của cậu làm ta muốn khóc đến mức suýt đổ cà phê ra bàn thí nghiệm. Thôi kệ, thí nghiệm cũng xong rồi."</t>
+          <t>"—Tình bạn của cậu làm tao muốn khóc đến mức suýt đổ cà phê ra bàn thí nghiệm. Thôi kệ, thí nghiệm cũng xong rồi."</t>
         </is>
       </c>
     </row>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Lỗi hệ thống à? Không, không, không phải đồng phục của ta!!</t>
+          <t>Lỗi hệ thống à? Không, không, không phải đồng phục của tao!!</t>
         </is>
       </c>
     </row>
@@ -13834,7 +13834,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Nhìn tay áo cậu kìa! Chính ta mới là người mắc nợ cậu.</t>
+          <t>Nhìn tay áo cậu kìa! Chính tao mới là người mắc nợ cậu.</t>
         </is>
       </c>
     </row>
@@ -13899,7 +13899,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Bói toán à... Hồi nhỏ ta mê mẩn cái này lắm.</t>
+          <t>Bói toán à... Hồi nhỏ tao mê mẩn cái này lắm.</t>
         </is>
       </c>
     </row>
@@ -14029,7 +14029,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Khi ta học được cách dự đoán kết quả bằng thuật toán, mọi thứ trở nên vô hồn. Giờ nó chỉ còn là một bài toán...</t>
+          <t>Khi tao học được cách dự đoán kết quả bằng thuật toán, mọi thứ trở nên vô hồn. Giờ nó chỉ còn là một bài toán...</t>
         </is>
       </c>
     </row>
@@ -14094,7 +14094,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Ta nghe nói giờ cậu còn bói toán trước khi bước vào phòng thí nghiệm nữa à?</t>
+          <t>Tao nghe nói giờ cậu còn bói toán trước khi bước vào phòng thí nghiệm nữa à?</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Cậu ngâm mình trong phòng thí nghiệm bao lâu rồi? Sắp thối đến nơi rồi đấy...</t>
+          <t>Mày ngâm mình trong phòng thí nghiệm bao lâu rồi? Sắp thối đến nơi rồi đấy...</t>
         </is>
       </c>
     </row>
@@ -14939,7 +14939,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>—Thôi, không tự lừa mình được nữa rồi. Ta phải về ký túc xá tắm ngay lập tức!</t>
+          <t>—Thôi, không tự lừa mình được nữa rồi. Tao phải về ký túc xá tắm ngay lập tức!</t>
         </is>
       </c>
     </row>
@@ -15004,7 +15004,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Tập luyện nhiều thế này khiến ta thèm món ăn quê nhà quá.</t>
+          <t>Tập luyện nhiều thế này khiến tao thèm món ăn quê nhà quá.</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Cậu nghiêm túc đấy à? Ai chẳng biết Ragunna nổi tiếng đồ ăn ngon? Đến dân Huanglong tụi ta còn biết Pizza Tropicale cơ mà!</t>
+          <t>Cậu nghiêm túc đấy à? Ai chẳng biết Ragunna nổi tiếng đồ ăn ngon? Đến dân Huanglong tụi tao còn biết Pizza Tropicale cơ mà!</t>
         </is>
       </c>
     </row>
@@ -16174,7 +16174,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Thôi bỏ đi, ta chỉ cần mua vài ống năng lượng thôi. Chẳng gì hiệu quả hơn...</t>
+          <t>Thôi bỏ đi, tao chỉ cần mua vài ống năng lượng thôi. Chẳng gì hiệu quả hơn...</t>
         </is>
       </c>
     </row>
@@ -16369,7 +16369,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Thằng cha nào trong cái hố đen kia lại đòi món hầm sơn hào hải vị giờ này?! Ta kiếm đâu ra bây giờ?!</t>
+          <t>Thằng cha nào trong cái hố đen kia lại đòi món hầm sơn hào hải vị giờ này?! Tao kiếm đâu ra bây giờ?!</t>
         </is>
       </c>
     </row>
@@ -17539,7 +17539,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Sao lại thế?</t>
+          <t>Sao cơ?</t>
         </is>
       </c>
     </row>
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Hoạt hình chứ còn gì! Chính anime mecha đã khơi dậy niềm đam mê máy móc trong ta. Đến lúc truyền lại ngọn lửa ấy rồi!</t>
+          <t>Hoạt hình chứ còn gì! Chính anime mecha đã khơi dậy niềm đam mê máy móc trong tao. Đến lúc truyền lại ngọn lửa ấy rồi!</t>
         </is>
       </c>
     </row>
@@ -18059,7 +18059,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Ta không thể làm được nữa. Thật sự không thể đứng dậy nổi. Lại 8 giờ sáng rồi, ta sắp chết mất thôi...</t>
+          <t>Tao không thể làm được nữa. Thật sự không thể đứng dậy nổi. Lại 8 giờ sáng rồi, tao sắp chết mất thôi...</t>
         </is>
       </c>
     </row>
